--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34336,7 +34336,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1307" t="n">
-        <v>5865859</v>
+        <v>5867500</v>
       </c>
       <c r="C1307" t="n">
         <v>20.2399997711182</v>
@@ -34354,6 +34354,32 @@
         <v>19.75</v>
       </c>
       <c r="H1307" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1308" t="n">
+        <v>16336264</v>
+      </c>
+      <c r="C1308" t="n">
+        <v>23.0450000762939</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>20.6299991607666</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>22.6100006103516</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>22.6100006103516</v>
+      </c>
+      <c r="H1308" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34362,7 +34362,7 @@
         <v>46279.5625</v>
       </c>
       <c r="B1308" t="n">
-        <v>16336264</v>
+        <v>16355700</v>
       </c>
       <c r="C1308" t="n">
         <v>23.0450000762939</v>
@@ -34380,6 +34380,32 @@
         <v>22.6100006103516</v>
       </c>
       <c r="H1308" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1309" t="n">
+        <v>9965125</v>
+      </c>
+      <c r="C1309" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>22.1506996154785</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>22.2700004577637</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>23.4799995422363</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>23.4799995422363</v>
+      </c>
+      <c r="H1309" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34388,13 +34388,13 @@
         <v>46280.5625</v>
       </c>
       <c r="B1309" t="n">
-        <v>9965125</v>
+        <v>9985300</v>
       </c>
       <c r="C1309" t="n">
         <v>23.625</v>
       </c>
       <c r="D1309" t="n">
-        <v>22.1506996154785</v>
+        <v>22.1509990692139</v>
       </c>
       <c r="E1309" t="n">
         <v>22.2700004577637</v>
@@ -34406,6 +34406,32 @@
         <v>23.4799995422363</v>
       </c>
       <c r="H1309" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1310" t="n">
+        <v>8328240</v>
+      </c>
+      <c r="C1310" t="n">
+        <v>23.9160995483398</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>23.0400009155273</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>23.1700000762939</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>23.1700000762939</v>
+      </c>
+      <c r="H1310" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34414,10 +34414,10 @@
         <v>46281.5625</v>
       </c>
       <c r="B1310" t="n">
-        <v>8328240</v>
+        <v>8360200</v>
       </c>
       <c r="C1310" t="n">
-        <v>23.9160995483398</v>
+        <v>23.9160003662109</v>
       </c>
       <c r="D1310" t="n">
         <v>22.8999996185303</v>
@@ -34432,6 +34432,32 @@
         <v>23.1700000762939</v>
       </c>
       <c r="H1310" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1311" t="n">
+        <v>14577575</v>
+      </c>
+      <c r="C1311" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>22.5881004333496</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>23.1900005340576</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>23.1900005340576</v>
+      </c>
+      <c r="H1311" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34440,13 +34440,13 @@
         <v>46282.5625</v>
       </c>
       <c r="B1311" t="n">
-        <v>14577575</v>
+        <v>14578300</v>
       </c>
       <c r="C1311" t="n">
-        <v>24.25</v>
+        <v>24.2549991607666</v>
       </c>
       <c r="D1311" t="n">
-        <v>22.5881004333496</v>
+        <v>22.5879993438721</v>
       </c>
       <c r="E1311" t="n">
         <v>22.75</v>
@@ -34458,6 +34458,32 @@
         <v>23.1900005340576</v>
       </c>
       <c r="H1311" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1312" t="n">
+        <v>12890304</v>
+      </c>
+      <c r="C1312" t="n">
+        <v>23.2248992919922</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>22.1786003112793</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>23.1299991607666</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>22.5100002288818</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>22.5100002288818</v>
+      </c>
+      <c r="H1312" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34466,13 +34466,13 @@
         <v>46283.5625</v>
       </c>
       <c r="B1312" t="n">
-        <v>12890304</v>
+        <v>13014900</v>
       </c>
       <c r="C1312" t="n">
-        <v>23.2248992919922</v>
+        <v>23.2250003814697</v>
       </c>
       <c r="D1312" t="n">
-        <v>22.1786003112793</v>
+        <v>22.1790008544922</v>
       </c>
       <c r="E1312" t="n">
         <v>23.1299991607666</v>
@@ -34484,6 +34484,32 @@
         <v>22.5100002288818</v>
       </c>
       <c r="H1312" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1313" t="n">
+        <v>8216313</v>
+      </c>
+      <c r="C1313" t="n">
+        <v>23.8050003051758</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>22.375</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>22.5900001525879</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="H1313" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34492,13 +34492,13 @@
         <v>46286.5625</v>
       </c>
       <c r="B1313" t="n">
-        <v>8216313</v>
+        <v>8219700</v>
       </c>
       <c r="C1313" t="n">
         <v>23.8050003051758</v>
       </c>
       <c r="D1313" t="n">
-        <v>22.375</v>
+        <v>22.3600006103516</v>
       </c>
       <c r="E1313" t="n">
         <v>22.5900001525879</v>
@@ -34510,6 +34510,32 @@
         <v>23.7999992370605</v>
       </c>
       <c r="H1313" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1314" t="n">
+        <v>7657878</v>
+      </c>
+      <c r="C1314" t="n">
+        <v>24.1700000762939</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>23.4200000762939</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>24.1700000762939</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>23.8500003814697</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>23.8500003814697</v>
+      </c>
+      <c r="H1314" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -30576,7 +30576,7 @@
         <v>46288.5625</v>
       </c>
       <c r="B1314" t="n">
-        <v>7327179</v>
+        <v>7328900</v>
       </c>
       <c r="C1314" t="n">
         <v>24.2999992370605</v>
@@ -30591,6 +30591,29 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1314" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1315" t="n">
+        <v>6065774</v>
+      </c>
+      <c r="C1315" t="n">
+        <v>24.3980007171631</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>23.8500003814697</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>23.9449996948242</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>23.9799995422363</v>
+      </c>
+      <c r="G1315" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34596,10 +34596,10 @@
         <v>46290.5625</v>
       </c>
       <c r="B1317" t="n">
-        <v>10444148</v>
+        <v>10460400</v>
       </c>
       <c r="C1317" t="n">
-        <v>24.2264003753662</v>
+        <v>24.2259998321533</v>
       </c>
       <c r="D1317" t="n">
         <v>22.2999992370605</v>
@@ -34614,6 +34614,32 @@
         <v>22.3799991607666</v>
       </c>
       <c r="H1317" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1318" t="n">
+        <v>6398541</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>23.0499992370605</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>21.7900009155273</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>21.8700008392334</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>22.7399997711182</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>22.7399997711182</v>
+      </c>
+      <c r="H1318" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34622,7 +34622,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1318" t="n">
-        <v>6398541</v>
+        <v>6400100</v>
       </c>
       <c r="C1318" t="n">
         <v>23.0499992370605</v>
@@ -34640,6 +34640,32 @@
         <v>22.7399997711182</v>
       </c>
       <c r="H1318" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1319" t="n">
+        <v>6993653</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>23.4150009155273</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>22.4699993133545</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>23.3099994659424</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>23.3099994659424</v>
+      </c>
+      <c r="H1319" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34648,7 +34648,7 @@
         <v>46294.5625</v>
       </c>
       <c r="B1319" t="n">
-        <v>6993653</v>
+        <v>6994200</v>
       </c>
       <c r="C1319" t="n">
         <v>23.4150009155273</v>
@@ -34666,6 +34666,32 @@
         <v>23.3099994659424</v>
       </c>
       <c r="H1319" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1320" t="n">
+        <v>8881828</v>
+      </c>
+      <c r="C1320" t="n">
+        <v>24.0599994659424</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>23.2359008789062</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>23.7600002288818</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>23.7600002288818</v>
+      </c>
+      <c r="H1320" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34674,13 +34674,13 @@
         <v>46295.5625</v>
       </c>
       <c r="B1320" t="n">
-        <v>8881828</v>
+        <v>8899300</v>
       </c>
       <c r="C1320" t="n">
         <v>24.0599994659424</v>
       </c>
       <c r="D1320" t="n">
-        <v>23.2359008789062</v>
+        <v>23.3810005187988</v>
       </c>
       <c r="E1320" t="n">
         <v>23.6000003814697</v>
@@ -34692,6 +34692,32 @@
         <v>23.7600002288818</v>
       </c>
       <c r="H1320" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1321" t="n">
+        <v>8958453</v>
+      </c>
+      <c r="C1321" t="n">
+        <v>24.6900005340576</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>23.4300003051758</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>24.1200008392334</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>24.6700000762939</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>24.6700000762939</v>
+      </c>
+      <c r="H1321" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34700,13 +34700,13 @@
         <v>46296.5625</v>
       </c>
       <c r="B1321" t="n">
-        <v>8958453</v>
+        <v>8961500</v>
       </c>
       <c r="C1321" t="n">
         <v>24.6900005340576</v>
       </c>
       <c r="D1321" t="n">
-        <v>23.4300003051758</v>
+        <v>23.4099998474121</v>
       </c>
       <c r="E1321" t="n">
         <v>24.1200008392334</v>
@@ -34718,6 +34718,32 @@
         <v>24.6700000762939</v>
       </c>
       <c r="H1321" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1322" t="n">
+        <v>11316282</v>
+      </c>
+      <c r="C1322" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>24.9200000762939</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>24.9200000762939</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>25.0599994659424</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>25.0599994659424</v>
+      </c>
+      <c r="H1322" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34726,7 +34726,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1322" t="n">
-        <v>11316282</v>
+        <v>11317600</v>
       </c>
       <c r="C1322" t="n">
         <v>25.75</v>
@@ -34744,6 +34744,32 @@
         <v>25.0599994659424</v>
       </c>
       <c r="H1322" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1323" t="n">
+        <v>8456716</v>
+      </c>
+      <c r="C1323" t="n">
+        <v>25.5100002288818</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>24.9500007629395</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>25.1599998474121</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>25.4300003051758</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>25.4300003051758</v>
+      </c>
+      <c r="H1323" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34752,7 +34752,7 @@
         <v>46300.5625</v>
       </c>
       <c r="B1323" t="n">
-        <v>8456716</v>
+        <v>8457900</v>
       </c>
       <c r="C1323" t="n">
         <v>25.5100002288818</v>
@@ -34770,6 +34770,32 @@
         <v>25.4300003051758</v>
       </c>
       <c r="H1323" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1324" t="n">
+        <v>9226037</v>
+      </c>
+      <c r="C1324" t="n">
+        <v>26.3349990844727</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>25.3299999237061</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>25.4200000762939</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="H1324" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34778,7 +34778,7 @@
         <v>46301.5625</v>
       </c>
       <c r="B1324" t="n">
-        <v>9226037</v>
+        <v>9227300</v>
       </c>
       <c r="C1324" t="n">
         <v>26.3349990844727</v>
@@ -34796,6 +34796,32 @@
         <v>25.7999992370605</v>
       </c>
       <c r="H1324" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1325" t="n">
+        <v>8035068</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>25.6200008392334</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>25.0699996948242</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>25.5200004577637</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>25.3099994659424</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>25.3099994659424</v>
+      </c>
+      <c r="H1325" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34804,7 +34804,7 @@
         <v>46302.5625</v>
       </c>
       <c r="B1325" t="n">
-        <v>8035068</v>
+        <v>8035800</v>
       </c>
       <c r="C1325" t="n">
         <v>25.6200008392334</v>
@@ -34822,6 +34822,32 @@
         <v>25.3099994659424</v>
       </c>
       <c r="H1325" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1326" t="n">
+        <v>7515091</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>25.6399993896484</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>25.2900009155273</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="H1326" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34830,7 +34830,7 @@
         <v>46303.5625</v>
       </c>
       <c r="B1326" t="n">
-        <v>7515091</v>
+        <v>7516400</v>
       </c>
       <c r="C1326" t="n">
         <v>25.6399993896484</v>
@@ -34848,6 +34848,32 @@
         <v>25.3999996185303</v>
       </c>
       <c r="H1326" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1327" t="n">
+        <v>7386603</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>25.7700004577637</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>26.2700004577637</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>26.2700004577637</v>
+      </c>
+      <c r="H1327" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34856,13 +34856,13 @@
         <v>46304.5625</v>
       </c>
       <c r="B1327" t="n">
-        <v>7386603</v>
+        <v>7389200</v>
       </c>
       <c r="C1327" t="n">
         <v>26.5</v>
       </c>
       <c r="D1327" t="n">
-        <v>25.5</v>
+        <v>25.4899997711182</v>
       </c>
       <c r="E1327" t="n">
         <v>25.7700004577637</v>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34908,10 +34908,10 @@
         <v>46308.5625</v>
       </c>
       <c r="B1329" t="n">
-        <v>27550058</v>
+        <v>27557500</v>
       </c>
       <c r="C1329" t="n">
-        <v>25.3476009368896</v>
+        <v>25.3479995727539</v>
       </c>
       <c r="D1329" t="n">
         <v>23.4599990844727</v>
@@ -34926,6 +34926,32 @@
         <v>24.0100002288818</v>
       </c>
       <c r="H1329" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1330" t="n">
+        <v>30537958</v>
+      </c>
+      <c r="C1330" t="n">
+        <v>23.7900009155273</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>22.7950000762939</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>23.6499996185303</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>22.8199996948242</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>22.8199996948242</v>
+      </c>
+      <c r="H1330" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34934,7 +34934,7 @@
         <v>46309.5625</v>
       </c>
       <c r="B1330" t="n">
-        <v>30537958</v>
+        <v>30616200</v>
       </c>
       <c r="C1330" t="n">
         <v>23.7900009155273</v>
@@ -34952,6 +34952,32 @@
         <v>22.8199996948242</v>
       </c>
       <c r="H1330" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1331" t="n">
+        <v>14218520</v>
+      </c>
+      <c r="C1331" t="n">
+        <v>23.4300003051758</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>22.1700000762939</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>22.3500003814697</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>23.3700008392334</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>23.3700008392334</v>
+      </c>
+      <c r="H1331" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -34960,7 +34960,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B1331" t="n">
-        <v>14218520</v>
+        <v>14756700</v>
       </c>
       <c r="C1331" t="n">
         <v>23.4300003051758</v>
@@ -34978,6 +34978,32 @@
         <v>23.3700008392334</v>
       </c>
       <c r="H1331" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1332" t="n">
+        <v>17647138</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>21.0799999237061</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>23.4500007629395</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>21.5799999237061</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>21.5799999237061</v>
+      </c>
+      <c r="H1332" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39000,7 +39000,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="H1332" t="n">
-        <v>17661000</v>
+        <v>17674100</v>
       </c>
       <c r="I1332" t="s">
         <v>9</v>
@@ -39029,9 +39029,38 @@
         <v>21.7099990844727</v>
       </c>
       <c r="H1333" t="n">
-        <v>9075192</v>
+        <v>9075500</v>
       </c>
       <c r="I1333" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1334" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>21.6200008392334</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>22.2749996185303</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>21.1900005340576</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>8541919</v>
+      </c>
+      <c r="I1334" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39058,9 +39058,38 @@
         <v>22</v>
       </c>
       <c r="H1334" t="n">
-        <v>8541919</v>
+        <v>8542600</v>
       </c>
       <c r="I1334" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1335" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>22.2199993133545</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>23.2399997711182</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>22.0849990844727</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>22.7700004577637</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>22.7700004577637</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>14398130</v>
+      </c>
+      <c r="I1335" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39078,7 +39078,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="E1335" t="n">
-        <v>22.0849990844727</v>
+        <v>22.0599994659424</v>
       </c>
       <c r="F1335" t="n">
         <v>22.7700004577637</v>
@@ -39087,9 +39087,38 @@
         <v>22.7700004577637</v>
       </c>
       <c r="H1335" t="n">
-        <v>14398130</v>
+        <v>14425700</v>
       </c>
       <c r="I1335" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1336" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>23.1350002288818</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>23.6499996185303</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>22.4337997436523</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>7955862</v>
+      </c>
+      <c r="I1336" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39107,7 +39107,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="E1336" t="n">
-        <v>22.4337997436523</v>
+        <v>22.4340000152588</v>
       </c>
       <c r="F1336" t="n">
         <v>22.5</v>
@@ -39116,9 +39116,38 @@
         <v>22.5</v>
       </c>
       <c r="H1336" t="n">
-        <v>7955862</v>
+        <v>7960600</v>
       </c>
       <c r="I1336" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1337" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>24.0650005340576</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>22.3099994659424</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>24</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>18422153</v>
+      </c>
+      <c r="I1337" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39133,10 +39133,10 @@
         <v>22.5</v>
       </c>
       <c r="D1337" t="n">
-        <v>24.0650005340576</v>
+        <v>24.0699996948242</v>
       </c>
       <c r="E1337" t="n">
-        <v>22.3099994659424</v>
+        <v>22.2999992370605</v>
       </c>
       <c r="F1337" t="n">
         <v>24</v>
@@ -39145,9 +39145,38 @@
         <v>24</v>
       </c>
       <c r="H1337" t="n">
-        <v>18422153</v>
+        <v>18424300</v>
       </c>
       <c r="I1337" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1338" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1338" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>25.5599994659424</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>24.1399993896484</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>12475472</v>
+      </c>
+      <c r="I1338" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39174,9 +39174,38 @@
         <v>25.5</v>
       </c>
       <c r="H1338" t="n">
-        <v>12475472</v>
+        <v>12495900</v>
       </c>
       <c r="I1338" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1339" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1339" t="n">
+        <v>25.2999992370605</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>25.8887996673584</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>25.2150001525879</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>25.6499996185303</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>25.6499996185303</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>9177645</v>
+      </c>
+      <c r="I1339" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39191,7 +39191,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="D1339" t="n">
-        <v>25.8887996673584</v>
+        <v>25.8899993896484</v>
       </c>
       <c r="E1339" t="n">
         <v>25.2150001525879</v>
@@ -39203,9 +39203,38 @@
         <v>25.6499996185303</v>
       </c>
       <c r="H1339" t="n">
-        <v>9177645</v>
+        <v>9180400</v>
       </c>
       <c r="I1339" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1340" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1340" t="n">
+        <v>25.5599994659424</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>26.076000213623</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>25.3899993896484</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>25.5900001525879</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>25.5900001525879</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>9320908</v>
+      </c>
+      <c r="I1340" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39232,9 +39232,38 @@
         <v>25.5900001525879</v>
       </c>
       <c r="H1340" t="n">
-        <v>9320908</v>
+        <v>9382700</v>
       </c>
       <c r="I1340" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1341" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1341" t="n">
+        <v>24.3099994659424</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>26.2099990844727</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>24.1900005340576</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>25.7099990844727</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>25.7099990844727</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>10977024</v>
+      </c>
+      <c r="I1341" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/S.xlsx
+++ b/data/S.xlsx
@@ -39261,9 +39261,38 @@
         <v>25.7099990844727</v>
       </c>
       <c r="H1341" t="n">
-        <v>10977024</v>
+        <v>11020200</v>
       </c>
       <c r="I1341" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1342" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1342" t="n">
+        <v>25.4699993133545</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>25.9050006866455</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>24.3449993133545</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>25.1499996185303</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>25.1499996185303</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>9991954</v>
+      </c>
+      <c r="I1342" t="s">
         <v>9</v>
       </c>
     </row>
